--- a/data/trans_orig/IP3106-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP3106-Provincia-trans_orig.xlsx
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3564</t>
+          <t>3585</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3541</t>
+          <t>3559</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1373</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7686</t>
+          <t>7672</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1369</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7981</t>
+          <t>8011</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4108</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12004</t>
+          <t>11830</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>5605</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15189</t>
+          <t>14829</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11220</t>
+          <t>11430</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>23896</t>
+          <t>23595</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>23,86%</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35541</t>
+          <t>35715</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>43330</t>
+          <t>43437</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31828</t>
+          <t>31787</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>42245</t>
+          <t>42044</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>70604</t>
+          <t>70419</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>84428</t>
+          <t>83545</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>84,49%</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3254</t>
+          <t>3859</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3949</t>
+          <t>3328</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7500</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>8311</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4190</t>
+          <t>4320</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12625</t>
+          <t>13210</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>652</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5758</t>
+          <t>6089</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>658</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2494</t>
+          <t>2491</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>10090</t>
+          <t>9764</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -2093,12 +2093,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>82330</t>
+          <t>82066</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>89802</t>
+          <t>89803</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2128,12 +2128,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>92840</t>
+          <t>93060</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>101051</t>
+          <t>101541</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2143,12 +2143,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>177683</t>
+          <t>177824</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>189433</t>
+          <t>189253</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2178,12 +2178,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,69%</t>
         </is>
       </c>
     </row>
@@ -2662,12 +2662,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3741</t>
+          <t>3754</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12952</t>
+          <t>12664</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2677,12 +2677,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1675</t>
+          <t>1249</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7264</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,12 +2732,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6148</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>16429</t>
+          <t>17215</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,39%</t>
         </is>
       </c>
     </row>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16677</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28783</t>
+          <t>28915</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,12 +2810,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>22196</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34951</t>
+          <t>35307</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>43076</t>
+          <t>42623</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>61514</t>
+          <t>61229</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>47,62%</t>
         </is>
       </c>
     </row>
@@ -2888,12 +2888,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>25801</t>
+          <t>26248</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>38671</t>
+          <t>38576</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2923,12 +2923,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>27074</t>
+          <t>27638</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>39928</t>
+          <t>40171</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2958,12 +2958,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>56873</t>
+          <t>56754</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>75559</t>
+          <t>76379</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>59,4%</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3374</t>
+          <t>3370</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4091</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -3457,12 +3457,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1458</t>
+          <t>1481</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8950</t>
+          <t>8164</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3472,12 +3472,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1619</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9295</t>
+          <t>9290</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3507,12 +3507,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4566</t>
+          <t>4085</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>14714</t>
+          <t>14465</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,95%</t>
         </is>
       </c>
     </row>
@@ -3570,12 +3570,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9924</t>
+          <t>9639</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>21121</t>
+          <t>21206</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3585,12 +3585,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10515</t>
+          <t>10026</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>22561</t>
+          <t>21794</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3620,12 +3620,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>21991</t>
+          <t>22414</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>39358</t>
+          <t>38775</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3655,12 +3655,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,66%</t>
         </is>
       </c>
     </row>
@@ -3683,12 +3683,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>45020</t>
+          <t>45184</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>56838</t>
+          <t>57070</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3698,49 +3698,49 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
+          <t>81,11%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>54281</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>47895</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>60642</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>72,31%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>63,8%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
           <t>80,78%</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>54281</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>47401</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>60114</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>72,31%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>63,14%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>80,08%</t>
-        </is>
-      </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>162</t>
@@ -3753,12 +3753,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>96116</t>
+          <t>95787</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>114870</t>
+          <t>114520</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>65,87%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>78,75%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3577</t>
+          <t>3603</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4800</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>4800</t>
+          <t>4530</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3606</t>
+          <t>3594</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>5143</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -4365,12 +4365,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>938</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6861</t>
+          <t>7068</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4380,12 +4380,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>694</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5641</t>
+          <t>5603</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>9221</t>
+          <t>9340</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,49%</t>
         </is>
       </c>
     </row>
@@ -4478,12 +4478,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>31507</t>
+          <t>30875</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>37973</t>
+          <t>37729</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4493,49 +4493,49 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
+          <t>96,05%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>38505</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>34919</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>40643</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>91,58%</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>83,05%</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
           <t>96,67%</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>38505</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>34255</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>40640</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>91,58%</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>81,47%</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>96,66%</t>
-        </is>
-      </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
           <t>107</t>
@@ -4548,12 +4548,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>68689</t>
+          <t>68843</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>77833</t>
+          <t>77547</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,35%</t>
         </is>
       </c>
     </row>
@@ -5047,12 +5047,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1932</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>8778</t>
+          <t>8985</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5062,12 +5062,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>3080</t>
+          <t>3103</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>9597</t>
+          <t>10084</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>6290</t>
+          <t>6038</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>15669</t>
+          <t>15501</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,04%</t>
         </is>
       </c>
     </row>
@@ -5160,12 +5160,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>14952</t>
+          <t>14824</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>26344</t>
+          <t>26212</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5195,12 +5195,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>14324</t>
+          <t>13716</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>25809</t>
+          <t>24954</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>31767</t>
+          <t>32650</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>47505</t>
+          <t>48907</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>44,29%</t>
         </is>
       </c>
     </row>
@@ -5273,12 +5273,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>21633</t>
+          <t>21361</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>33281</t>
+          <t>33300</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5288,12 +5288,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5308,12 +5308,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>26713</t>
+          <t>26989</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>37926</t>
+          <t>38379</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5323,12 +5323,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5343,12 +5343,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>51213</t>
+          <t>51545</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>68375</t>
+          <t>68805</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>62,31%</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>4332</t>
+          <t>3887</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>3635</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>2859</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5769,7 +5769,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>5084</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -5842,12 +5842,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>4932</t>
+          <t>4826</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>15061</t>
+          <t>14487</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5857,12 +5857,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5877,12 +5877,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>5510</t>
+          <t>5651</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>15568</t>
+          <t>15527</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5912,12 +5912,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>13235</t>
+          <t>12932</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>27219</t>
+          <t>26400</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5927,12 +5927,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -5955,12 +5955,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>21307</t>
+          <t>21167</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>36859</t>
+          <t>37104</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5990,12 +5990,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>25346</t>
+          <t>25322</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>41405</t>
+          <t>41130</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6005,12 +6005,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6025,12 +6025,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>50597</t>
+          <t>50595</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>72572</t>
+          <t>73093</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,51%</t>
         </is>
       </c>
     </row>
@@ -6068,12 +6068,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>74776</t>
+          <t>74433</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>92187</t>
+          <t>92145</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>61,1%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>73250</t>
+          <t>73211</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>90944</t>
+          <t>90690</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6118,12 +6118,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6138,12 +6138,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>153032</t>
+          <t>153524</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>177765</t>
+          <t>177002</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6153,12 +6153,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,47%</t>
         </is>
       </c>
     </row>
@@ -6637,12 +6637,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>7257</t>
+          <t>7509</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6652,12 +6652,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6672,12 +6672,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>601</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>5376</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6687,12 +6687,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6707,12 +6707,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>2509</t>
+          <t>2556</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>9567</t>
+          <t>10485</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -6750,12 +6750,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>8528</t>
+          <t>8771</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>19286</t>
+          <t>19928</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6765,12 +6765,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6785,12 +6785,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>6379</t>
+          <t>6062</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>16255</t>
+          <t>16081</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>17367</t>
+          <t>17149</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>32433</t>
+          <t>32049</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,7%</t>
         </is>
       </c>
     </row>
@@ -6863,12 +6863,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>123607</t>
+          <t>122678</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>135390</t>
+          <t>135426</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6878,12 +6878,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>134399</t>
+          <t>134754</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>145016</t>
+          <t>145090</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>261210</t>
+          <t>261260</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>278340</t>
+          <t>278230</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,85%</t>
         </is>
       </c>
     </row>
@@ -7241,12 +7241,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>671</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>6532</t>
+          <t>6254</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7256,12 +7256,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>669</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>6980</t>
+          <t>6254</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7296,7 +7296,7 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -7324,7 +7324,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>3880</t>
+          <t>3736</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7339,7 +7339,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>4759</t>
+          <t>4216</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>649</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>5530</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,42%</t>
         </is>
       </c>
     </row>
@@ -7432,12 +7432,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>24700</t>
+          <t>24719</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>42623</t>
+          <t>43801</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -7467,12 +7467,12 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>24999</t>
+          <t>24627</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>44372</t>
+          <t>42788</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>55178</t>
+          <t>54611</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>82079</t>
+          <t>80981</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -7545,12 +7545,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>96917</t>
+          <t>97225</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>127736</t>
+          <t>126981</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7580,12 +7580,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>105912</t>
+          <t>105849</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>136995</t>
+          <t>137523</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>212908</t>
+          <t>212776</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>257466</t>
+          <t>258197</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,71%</t>
         </is>
       </c>
     </row>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>471486</t>
+          <t>471538</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>504997</t>
+          <t>503844</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7693,12 +7693,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>497848</t>
+          <t>499662</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>532869</t>
+          <t>533140</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -7708,12 +7708,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7728,12 +7728,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>979215</t>
+          <t>979893</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>1030657</t>
+          <t>1027893</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7743,12 +7743,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,48%</t>
         </is>
       </c>
     </row>
@@ -8355,7 +8355,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2557</t>
+          <t>2971</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4522</t>
+          <t>5471</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8425,7 +8425,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8440,7 +8440,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -8463,12 +8463,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10351</t>
+          <t>10896</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8498,12 +8498,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9799</t>
+          <t>9186</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8513,12 +8513,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5572</t>
+          <t>5463</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17314</t>
+          <t>16055</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8548,12 +8548,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>13,95%</t>
         </is>
       </c>
     </row>
@@ -8576,12 +8576,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2663</t>
+          <t>2572</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9852</t>
+          <t>10441</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8611,12 +8611,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2985</t>
+          <t>2810</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11377</t>
+          <t>11115</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8646,12 +8646,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7286</t>
+          <t>7591</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>19236</t>
+          <t>19283</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,75%</t>
         </is>
       </c>
     </row>
@@ -8689,12 +8689,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37186</t>
+          <t>36940</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>47030</t>
+          <t>47125</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8704,12 +8704,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8724,12 +8724,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>43136</t>
+          <t>43246</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>54179</t>
+          <t>53685</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8739,12 +8739,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>83748</t>
+          <t>83323</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>98352</t>
+          <t>97897</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,05%</t>
         </is>
       </c>
     </row>
@@ -9298,7 +9298,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4932</t>
+          <t>6635</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7432</t>
+          <t>5686</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9348,7 +9348,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -9406,12 +9406,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>646</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9421,12 +9421,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9441,12 +9441,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>649</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>5836</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9456,12 +9456,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -9519,12 +9519,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>88307</t>
+          <t>89610</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>96519</t>
+          <t>96521</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -9554,12 +9554,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>184899</t>
+          <t>184875</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>191894</t>
+          <t>192478</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9569,12 +9569,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3359</t>
+          <t>3065</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9902,7 +9902,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3423</t>
+          <t>3395</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9917,7 +9917,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -10053,12 +10053,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>777</t>
+          <t>776</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7326</t>
+          <t>7014</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10068,12 +10068,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>759</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>6965</t>
+          <t>6951</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -10166,12 +10166,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>648</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5856</t>
+          <t>5997</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10181,12 +10181,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10206,7 +10206,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4206</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10221,7 +10221,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10236,12 +10236,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8097</t>
+          <t>7756</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -10279,12 +10279,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>53743</t>
+          <t>53440</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>61178</t>
+          <t>61180</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10294,12 +10294,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10314,12 +10314,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>60267</t>
+          <t>60318</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>65055</t>
+          <t>65063</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10329,12 +10329,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10349,12 +10349,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>116760</t>
+          <t>116537</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>125562</t>
+          <t>125389</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10364,12 +10364,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,1%</t>
         </is>
       </c>
     </row>
@@ -10775,7 +10775,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>3077</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10790,7 +10790,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -10810,7 +10810,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>3235</t>
+          <t>3237</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10848,12 +10848,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1048</t>
+          <t>1068</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6260</t>
+          <t>6681</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10863,12 +10863,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4726</t>
+          <t>4738</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10918,12 +10918,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1931</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9326</t>
+          <t>8651</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10938,7 +10938,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -10961,12 +10961,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>5668</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14646</t>
+          <t>15587</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10976,12 +10976,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10996,12 +10996,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6021</t>
+          <t>6502</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>17547</t>
+          <t>17244</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -11011,12 +11011,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -11031,12 +11031,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>14211</t>
+          <t>14192</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>29068</t>
+          <t>28207</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -11046,12 +11046,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,42%</t>
         </is>
       </c>
     </row>
@@ -11074,12 +11074,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>55146</t>
+          <t>53757</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>64697</t>
+          <t>64642</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11089,12 +11089,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11109,12 +11109,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>60784</t>
+          <t>60753</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>72520</t>
+          <t>72087</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11124,12 +11124,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11144,12 +11144,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>118798</t>
+          <t>119241</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>134076</t>
+          <t>134357</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11159,12 +11159,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,76%</t>
         </is>
       </c>
     </row>
@@ -11761,7 +11761,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3326</t>
+          <t>3486</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -11776,7 +11776,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -11831,7 +11831,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>3485</t>
+          <t>3446</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -11846,7 +11846,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -11869,7 +11869,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>38598</t>
+          <t>38438</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -11884,7 +11884,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -11939,7 +11939,7 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>84516</t>
+          <t>84555</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
@@ -11954,7 +11954,7 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -12330,7 +12330,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>4472</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -12345,7 +12345,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -12400,7 +12400,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>3727</t>
+          <t>4429</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -12415,7 +12415,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -12438,12 +12438,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>7237</t>
+          <t>7022</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -12453,12 +12453,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -12478,7 +12478,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3980</t>
+          <t>3547</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -12493,7 +12493,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -12508,12 +12508,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1707</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>8750</t>
+          <t>8787</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -12523,12 +12523,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -12556,7 +12556,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>4746</t>
+          <t>5334</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -12571,7 +12571,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -12586,12 +12586,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1548</t>
+          <t>1780</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>9594</t>
+          <t>9669</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -12601,12 +12601,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -12621,12 +12621,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2976</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>11795</t>
+          <t>11848</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -12636,12 +12636,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,74%</t>
         </is>
       </c>
     </row>
@@ -12664,12 +12664,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>38763</t>
+          <t>38742</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>46484</t>
+          <t>46429</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -12679,12 +12679,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -12699,12 +12699,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>41231</t>
+          <t>41173</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>49577</t>
+          <t>49636</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -12714,12 +12714,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -12734,12 +12734,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>83295</t>
+          <t>83482</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>94385</t>
+          <t>94276</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -12749,12 +12749,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,39%</t>
         </is>
       </c>
     </row>
@@ -13160,7 +13160,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>6109</t>
+          <t>4632</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -13175,7 +13175,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -13195,7 +13195,7 @@
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>4769</t>
+          <t>5659</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -13210,7 +13210,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -13233,12 +13233,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>727</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>6687</t>
+          <t>6998</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -13248,12 +13248,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -13268,12 +13268,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>4034</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>12132</t>
+          <t>12862</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -13283,12 +13283,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -13303,12 +13303,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>6078</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>15542</t>
+          <t>16357</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -13318,12 +13318,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -13346,12 +13346,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>3389</t>
+          <t>3744</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>12468</t>
+          <t>12691</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -13381,12 +13381,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>7870</t>
+          <t>7513</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>19520</t>
+          <t>18334</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -13396,12 +13396,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -13416,12 +13416,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>13268</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>27327</t>
+          <t>27543</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -13431,12 +13431,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,98%</t>
         </is>
       </c>
     </row>
@@ -13459,12 +13459,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>107181</t>
+          <t>106795</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>117276</t>
+          <t>117146</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -13474,12 +13474,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -13494,12 +13494,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>99368</t>
+          <t>100433</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>112976</t>
+          <t>113030</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -13509,12 +13509,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -13529,12 +13529,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>210781</t>
+          <t>211140</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>228006</t>
+          <t>227499</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -13544,12 +13544,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,7%</t>
         </is>
       </c>
     </row>
@@ -14033,7 +14033,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>3759</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -14048,7 +14048,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -14063,12 +14063,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>774</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>5458</t>
+          <t>6255</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -14083,7 +14083,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -14098,12 +14098,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>781</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>8166</t>
+          <t>7294</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -14113,12 +14113,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -14141,12 +14141,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>5341</t>
+          <t>4957</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>15212</t>
+          <t>14910</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -14156,12 +14156,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -14176,12 +14176,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>5087</t>
+          <t>5727</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>14959</t>
+          <t>15095</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -14191,12 +14191,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -14211,12 +14211,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>12000</t>
+          <t>12559</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>25217</t>
+          <t>26547</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -14226,12 +14226,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -14254,12 +14254,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>137587</t>
+          <t>137771</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>148033</t>
+          <t>148525</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -14269,12 +14269,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -14289,12 +14289,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>142441</t>
+          <t>141635</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>153430</t>
+          <t>152672</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -14304,12 +14304,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -14324,12 +14324,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>284614</t>
+          <t>282734</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>299400</t>
+          <t>299031</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -14339,12 +14339,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,11%</t>
         </is>
       </c>
     </row>
@@ -14637,7 +14637,7 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>2958</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -14652,7 +14652,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -14672,7 +14672,7 @@
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>3360</t>
+          <t>3829</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -14687,7 +14687,7 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,28%</t>
         </is>
       </c>
     </row>
@@ -14715,7 +14715,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>4223</t>
+          <t>4499</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -14730,7 +14730,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -14745,12 +14745,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>7189</t>
+          <t>6693</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -14760,12 +14760,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -14780,12 +14780,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>1491</t>
+          <t>1422</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>8273</t>
+          <t>8446</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -14800,7 +14800,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -14823,12 +14823,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>12123</t>
+          <t>11909</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>26939</t>
+          <t>26770</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -14838,12 +14838,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -14858,12 +14858,12 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>11831</t>
+          <t>11664</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>26107</t>
+          <t>27221</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -14873,12 +14873,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -14893,12 +14893,12 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>26939</t>
+          <t>27401</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>48615</t>
+          <t>47944</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -14908,12 +14908,12 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -14936,12 +14936,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>26619</t>
+          <t>25961</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>45231</t>
+          <t>44887</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -14951,12 +14951,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -14971,12 +14971,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>36811</t>
+          <t>37679</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>60017</t>
+          <t>59484</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -14986,12 +14986,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -15006,12 +15006,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>69091</t>
+          <t>68323</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>96673</t>
+          <t>97743</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -15021,12 +15021,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -15049,12 +15049,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>586091</t>
+          <t>587242</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>609739</t>
+          <t>611351</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -15064,12 +15064,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -15084,12 +15084,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>607228</t>
+          <t>607965</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>634470</t>
+          <t>634885</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -15099,12 +15099,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -15119,12 +15119,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>1203301</t>
+          <t>1202947</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>1237696</t>
+          <t>1237592</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -15781,7 +15781,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4697</t>
+          <t>4242</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -15796,7 +15796,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -15816,7 +15816,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4062</t>
+          <t>4069</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -15854,12 +15854,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1182</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7397</t>
+          <t>9012</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -15874,7 +15874,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -15889,12 +15889,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>581</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5497</t>
+          <t>5967</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -15904,12 +15904,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -15924,12 +15924,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2702</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10785</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -15939,12 +15939,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -15967,12 +15967,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>825</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7031</t>
+          <t>7261</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -15982,12 +15982,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -16002,12 +16002,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2590</t>
+          <t>2561</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10204</t>
+          <t>9961</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -16017,12 +16017,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -16037,12 +16037,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4981</t>
+          <t>4740</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14637</t>
+          <t>14048</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -16052,12 +16052,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>11,79%</t>
         </is>
       </c>
     </row>
@@ -16080,12 +16080,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45340</t>
+          <t>44737</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>53806</t>
+          <t>53701</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -16095,12 +16095,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -16115,12 +16115,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48289</t>
+          <t>48039</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>57293</t>
+          <t>57285</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -16130,12 +16130,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -16150,12 +16150,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>97533</t>
+          <t>97917</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>109302</t>
+          <t>109542</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -16165,12 +16165,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,92%</t>
         </is>
       </c>
     </row>
@@ -16767,7 +16767,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3590</t>
+          <t>3731</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -16782,7 +16782,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -16797,12 +16797,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1495</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8895</t>
+          <t>8449</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -16812,12 +16812,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -16832,12 +16832,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1558</t>
+          <t>1574</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>9657</t>
+          <t>9205</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -16847,12 +16847,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -16875,7 +16875,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>93643</t>
+          <t>93502</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -16890,7 +16890,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -16910,12 +16910,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>95461</t>
+          <t>95907</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>102861</t>
+          <t>103010</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -16925,12 +16925,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -16945,12 +16945,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>191932</t>
+          <t>192384</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>200031</t>
+          <t>200015</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -17557,12 +17557,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>764</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5796</t>
+          <t>6578</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -17577,7 +17577,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -17592,12 +17592,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1531</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8820</t>
+          <t>8998</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -17607,12 +17607,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -17627,12 +17627,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3426</t>
+          <t>3013</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11978</t>
+          <t>11419</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -17670,12 +17670,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>53249</t>
+          <t>52467</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>58284</t>
+          <t>58281</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -17685,7 +17685,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>56961</t>
+          <t>56783</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>64250</t>
+          <t>63811</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -17720,12 +17720,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -17740,12 +17740,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>112848</t>
+          <t>113407</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>121400</t>
+          <t>121813</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -17755,12 +17755,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -18131,7 +18131,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4441</t>
+          <t>3937</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -18146,7 +18146,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -18201,7 +18201,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>5420</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -18216,7 +18216,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -18239,12 +18239,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>2836</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9920</t>
+          <t>10318</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -18254,12 +18254,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -18274,12 +18274,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>2064</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10219</t>
+          <t>10211</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -18289,12 +18289,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -18309,12 +18309,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6495</t>
+          <t>6384</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>17264</t>
+          <t>17062</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -18324,12 +18324,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,53%</t>
         </is>
       </c>
     </row>
@@ -18352,12 +18352,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2341</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10098</t>
+          <t>9685</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -18367,12 +18367,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -18387,12 +18387,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1954</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8912</t>
+          <t>9412</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -18402,12 +18402,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -18422,12 +18422,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5201</t>
+          <t>5229</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>15385</t>
+          <t>15141</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -18437,12 +18437,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -18465,12 +18465,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>53761</t>
+          <t>53666</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>63178</t>
+          <t>63508</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -18480,12 +18480,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -18500,12 +18500,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>62374</t>
+          <t>62033</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>72042</t>
+          <t>72307</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -18515,12 +18515,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -18535,12 +18535,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>119461</t>
+          <t>119027</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>133419</t>
+          <t>133184</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -18550,12 +18550,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,0%</t>
         </is>
       </c>
     </row>
@@ -19039,7 +19039,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>4205</t>
+          <t>3692</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -19069,12 +19069,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>607</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>6834</t>
+          <t>7302</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -19104,12 +19104,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>782</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7469</t>
+          <t>8296</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -19119,12 +19119,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -19147,12 +19147,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>11644</t>
+          <t>11667</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -19162,12 +19162,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -19182,12 +19182,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>1527</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>8528</t>
+          <t>8730</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -19217,12 +19217,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>6542</t>
+          <t>6540</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>16773</t>
+          <t>17485</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -19237,7 +19237,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>21,27%</t>
         </is>
       </c>
     </row>
@@ -19260,12 +19260,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>28825</t>
+          <t>29081</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>37523</t>
+          <t>37533</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -19275,12 +19275,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -19295,12 +19295,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>29294</t>
+          <t>29577</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>37335</t>
+          <t>37472</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -19310,12 +19310,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -19330,12 +19330,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>61365</t>
+          <t>61373</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>73566</t>
+          <t>73301</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -19345,12 +19345,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,18%</t>
         </is>
       </c>
     </row>
@@ -19756,7 +19756,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>3292</t>
+          <t>3830</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -19771,7 +19771,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -19791,7 +19791,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>4026</t>
+          <t>4025</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -19829,12 +19829,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>722</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>6394</t>
+          <t>6540</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -19844,12 +19844,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -19864,12 +19864,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2608</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>11275</t>
+          <t>11905</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -19879,12 +19879,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -19899,12 +19899,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>4662</t>
+          <t>4688</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>14817</t>
+          <t>15183</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -19914,12 +19914,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,71%</t>
         </is>
       </c>
     </row>
@@ -19942,12 +19942,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>16088</t>
+          <t>16237</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>27782</t>
+          <t>28295</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -19957,12 +19957,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -19977,12 +19977,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>14076</t>
+          <t>14313</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>26687</t>
+          <t>27511</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -19992,12 +19992,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -20012,12 +20012,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>33914</t>
+          <t>33292</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>50819</t>
+          <t>50437</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -20027,12 +20027,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>48,85%</t>
         </is>
       </c>
     </row>
@@ -20055,12 +20055,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>19511</t>
+          <t>18999</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>30937</t>
+          <t>31076</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -20070,12 +20070,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -20090,12 +20090,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>20593</t>
+          <t>19850</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>33061</t>
+          <t>32970</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -20105,12 +20105,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -20125,12 +20125,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>42345</t>
+          <t>43054</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>59674</t>
+          <t>60570</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -20140,12 +20140,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>58,67%</t>
         </is>
       </c>
     </row>
@@ -20624,12 +20624,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>7852</t>
+          <t>7148</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -20639,12 +20639,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -20659,12 +20659,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>7791</t>
+          <t>7822</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -20674,12 +20674,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -20694,12 +20694,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>3394</t>
+          <t>3358</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>12192</t>
+          <t>11801</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -20709,12 +20709,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -20737,12 +20737,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>8714</t>
+          <t>8695</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>20589</t>
+          <t>19479</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -20752,82 +20752,82 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
+          <t>6,93%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>15,53%</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>12082</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>7659</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>18526</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>9,14%</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>5,79%</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>14,01%</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>25660</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>17916</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t>33896</t>
+        </is>
+      </c>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>9,96%</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
           <t>6,95%</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>16,42%</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>12082</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>7586</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>18733</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="inlineStr">
-        <is>
-          <t>9,14%</t>
-        </is>
-      </c>
-      <c r="O50" s="2" t="inlineStr">
-        <is>
-          <t>5,74%</t>
-        </is>
-      </c>
-      <c r="P50" s="2" t="inlineStr">
-        <is>
-          <t>14,17%</t>
-        </is>
-      </c>
-      <c r="Q50" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="R50" s="2" t="inlineStr">
-        <is>
-          <t>25660</t>
-        </is>
-      </c>
-      <c r="S50" s="2" t="inlineStr">
-        <is>
-          <t>18170</t>
-        </is>
-      </c>
-      <c r="T50" s="2" t="inlineStr">
-        <is>
-          <t>35093</t>
-        </is>
-      </c>
-      <c r="U50" s="2" t="inlineStr">
-        <is>
-          <t>9,96%</t>
-        </is>
-      </c>
-      <c r="V50" s="2" t="inlineStr">
-        <is>
-          <t>7,05%</t>
-        </is>
-      </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,15%</t>
         </is>
       </c>
     </row>
@@ -20850,12 +20850,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>100964</t>
+          <t>101720</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>113872</t>
+          <t>114069</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -20865,12 +20865,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -20885,12 +20885,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>109344</t>
+          <t>109539</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>121876</t>
+          <t>121953</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -20900,12 +20900,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -20920,12 +20920,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>215837</t>
+          <t>216758</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>233926</t>
+          <t>233718</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -20935,12 +20935,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,71%</t>
         </is>
       </c>
     </row>
@@ -21326,7 +21326,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -21346,7 +21346,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>3587</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -21361,7 +21361,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -21381,7 +21381,7 @@
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>4196</t>
+          <t>4159</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -21396,7 +21396,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -21424,7 +21424,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>4245</t>
+          <t>4155</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -21439,7 +21439,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -21454,12 +21454,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>7716</t>
+          <t>7734</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -21469,12 +21469,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -21489,12 +21489,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>2488</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>9813</t>
+          <t>9507</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -21509,7 +21509,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -21532,12 +21532,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>12374</t>
+          <t>12162</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>24855</t>
+          <t>24427</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -21547,12 +21547,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -21567,12 +21567,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>8997</t>
+          <t>8562</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>20627</t>
+          <t>19888</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -21582,12 +21582,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -21602,12 +21602,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>23874</t>
+          <t>24007</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>39919</t>
+          <t>41079</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -21617,12 +21617,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,22%</t>
         </is>
       </c>
     </row>
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>123826</t>
+          <t>124809</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>137217</t>
+          <t>136988</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -21660,12 +21660,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -21680,12 +21680,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>133722</t>
+          <t>134907</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>146987</t>
+          <t>147561</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -21695,12 +21695,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -21715,12 +21715,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>263455</t>
+          <t>262501</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>281383</t>
+          <t>280897</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -21730,12 +21730,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,39%</t>
         </is>
       </c>
     </row>
@@ -22106,7 +22106,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>4831</t>
+          <t>5104</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -22121,7 +22121,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -22136,12 +22136,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>666</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>6160</t>
+          <t>6247</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -22156,7 +22156,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -22176,7 +22176,7 @@
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>8814</t>
+          <t>8056</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -22191,7 +22191,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -22214,12 +22214,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>11853</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>24808</t>
+          <t>24576</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -22229,12 +22229,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -22249,12 +22249,12 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>16013</t>
+          <t>15953</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>32355</t>
+          <t>31679</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -22264,12 +22264,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -22284,12 +22284,12 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>30181</t>
+          <t>31093</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>52449</t>
+          <t>52231</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -22299,12 +22299,12 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -22327,12 +22327,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>60034</t>
+          <t>59004</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>84867</t>
+          <t>84980</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -22342,12 +22342,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -22362,12 +22362,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>56995</t>
+          <t>56309</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>82864</t>
+          <t>83322</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -22377,12 +22377,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -22397,12 +22397,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>121661</t>
+          <t>121350</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>158124</t>
+          <t>158034</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -22412,12 +22412,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -22440,12 +22440,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>547148</t>
+          <t>547300</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>575405</t>
+          <t>576086</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -22455,12 +22455,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -22475,12 +22475,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>588596</t>
+          <t>587283</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>618102</t>
+          <t>616983</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -22490,12 +22490,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -22510,12 +22510,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>1143914</t>
+          <t>1143461</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>1184135</t>
+          <t>1185296</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -22525,12 +22525,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,97%</t>
         </is>
       </c>
     </row>
@@ -23363,7 +23363,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4595</t>
+          <t>5179</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -23378,7 +23378,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -23393,12 +23393,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9193</t>
+          <t>9366</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -23408,12 +23408,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -23428,12 +23428,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2101</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11724</t>
+          <t>10819</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -23443,12 +23443,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -23471,7 +23471,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66805</t>
+          <t>66221</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -23486,7 +23486,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -23506,12 +23506,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>65414</t>
+          <t>65241</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>73072</t>
+          <t>73300</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -23521,12 +23521,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -23541,12 +23541,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>134283</t>
+          <t>135188</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>143906</t>
+          <t>143890</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -23556,12 +23556,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,55%</t>
         </is>
       </c>
     </row>
@@ -24040,12 +24040,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7773</t>
+          <t>8226</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -24055,12 +24055,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5909</t>
+          <t>5468</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17927</t>
+          <t>18016</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -24090,12 +24090,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -24110,12 +24110,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8283</t>
+          <t>8021</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23233</t>
+          <t>22695</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -24125,12 +24125,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -24153,12 +24153,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32529</t>
+          <t>32415</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>88677</t>
+          <t>96106</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -24168,12 +24168,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -24188,12 +24188,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23208</t>
+          <t>23425</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>46212</t>
+          <t>45752</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -24203,12 +24203,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -24223,12 +24223,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>62876</t>
+          <t>63843</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>146834</t>
+          <t>139466</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>55,33%</t>
         </is>
       </c>
     </row>
@@ -24266,12 +24266,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34390</t>
+          <t>28079</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>89010</t>
+          <t>88907</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -24281,12 +24281,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -24301,12 +24301,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>69773</t>
+          <t>70703</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>93325</t>
+          <t>93435</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -24316,12 +24316,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -24336,12 +24336,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>96321</t>
+          <t>104958</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>173712</t>
+          <t>173292</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -24351,12 +24351,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>68,75%</t>
         </is>
       </c>
     </row>
@@ -24727,7 +24727,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3799</t>
+          <t>3350</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -24742,7 +24742,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -24757,12 +24757,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>584</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5883</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -24772,12 +24772,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -24792,12 +24792,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1147</t>
+          <t>1208</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6934</t>
+          <t>6930</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -24807,7 +24807,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -24835,12 +24835,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8458</t>
+          <t>7757</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -24850,12 +24850,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -24870,12 +24870,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6950</t>
+          <t>7154</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16182</t>
+          <t>16911</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -24885,12 +24885,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -24905,12 +24905,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>9995</t>
+          <t>10498</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>21774</t>
+          <t>22319</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -24920,12 +24920,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,57%</t>
         </is>
       </c>
     </row>
@@ -24948,12 +24948,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8444</t>
+          <t>8063</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17576</t>
+          <t>17341</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -24963,12 +24963,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -24983,12 +24983,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7654</t>
+          <t>7337</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18219</t>
+          <t>17670</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -24998,12 +24998,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -25018,12 +25018,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17929</t>
+          <t>18113</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>31516</t>
+          <t>31778</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -25033,12 +25033,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,44%</t>
         </is>
       </c>
     </row>
@@ -25061,12 +25061,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>32534</t>
+          <t>32298</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>42572</t>
+          <t>42788</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -25076,12 +25076,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>58,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -25096,12 +25096,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>33178</t>
+          <t>33083</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>45603</t>
+          <t>45563</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -25111,12 +25111,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -25131,12 +25131,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>69427</t>
+          <t>68214</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>85733</t>
+          <t>85586</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -25146,12 +25146,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>56,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>71,21%</t>
         </is>
       </c>
     </row>
@@ -25522,7 +25522,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3597</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -25537,7 +25537,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -25592,7 +25592,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>3314</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -25607,7 +25607,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -25630,12 +25630,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>481</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5666</t>
+          <t>5342</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -25645,12 +25645,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -25665,12 +25665,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3199</t>
+          <t>3354</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17120</t>
+          <t>17132</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -25680,12 +25680,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -25700,12 +25700,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5542</t>
+          <t>5531</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>20184</t>
+          <t>19378</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -25715,12 +25715,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,41%</t>
         </is>
       </c>
     </row>
@@ -25743,12 +25743,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1382</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9850</t>
+          <t>9699</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -25758,12 +25758,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -25783,7 +25783,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7881</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -25798,7 +25798,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -25813,12 +25813,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2339</t>
+          <t>2613</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>13370</t>
+          <t>14360</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -25828,12 +25828,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -25856,12 +25856,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>57013</t>
+          <t>56661</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>65972</t>
+          <t>66208</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -25871,12 +25871,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -25891,12 +25891,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>55612</t>
+          <t>55763</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>70327</t>
+          <t>70178</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -25906,12 +25906,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -25926,12 +25926,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>116362</t>
+          <t>115776</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>133400</t>
+          <t>133580</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -25941,12 +25941,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,45%</t>
         </is>
       </c>
     </row>
@@ -26543,7 +26543,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3326</t>
+          <t>3224</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -26558,7 +26558,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -26578,7 +26578,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4588</t>
+          <t>4223</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -26593,7 +26593,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -26608,12 +26608,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>359</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5938</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -26623,12 +26623,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -26651,7 +26651,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>30874</t>
+          <t>30976</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -26666,7 +26666,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -26686,7 +26686,7 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>36131</t>
+          <t>36496</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -26701,7 +26701,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -26721,12 +26721,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>68981</t>
+          <t>69627</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>74550</t>
+          <t>74560</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -26736,12 +26736,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -27107,12 +27107,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>740</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>6270</t>
+          <t>6484</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -27122,12 +27122,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -27147,7 +27147,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>11521</t>
+          <t>9360</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -27162,7 +27162,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -27177,12 +27177,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>12170</t>
+          <t>12675</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -27192,12 +27192,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,92%</t>
         </is>
       </c>
     </row>
@@ -27220,12 +27220,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>8048</t>
+          <t>8412</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>17381</t>
+          <t>17211</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -27235,12 +27235,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -27255,12 +27255,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>10998</t>
+          <t>10680</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>22177</t>
+          <t>22400</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -27270,12 +27270,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -27290,12 +27290,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>22041</t>
+          <t>22117</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>35828</t>
+          <t>35909</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -27305,12 +27305,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,62%</t>
         </is>
       </c>
     </row>
@@ -27333,12 +27333,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>15949</t>
+          <t>15307</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>25825</t>
+          <t>26051</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -27348,12 +27348,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -27368,12 +27368,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>18568</t>
+          <t>17955</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>30402</t>
+          <t>30570</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -27383,12 +27383,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>56,84%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -27403,12 +27403,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>37292</t>
+          <t>36996</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>53540</t>
+          <t>52864</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -27418,12 +27418,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>53,9%</t>
         </is>
       </c>
     </row>
@@ -27446,12 +27446,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>4970</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>12830</t>
+          <t>12902</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -27461,12 +27461,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -27481,12 +27481,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>6612</t>
+          <t>6673</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>15803</t>
+          <t>15692</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -27496,12 +27496,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -27516,12 +27516,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>13796</t>
+          <t>13671</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>26030</t>
+          <t>26002</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -27531,12 +27531,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,51%</t>
         </is>
       </c>
     </row>
@@ -28015,12 +28015,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>1733</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>9031</t>
+          <t>9167</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -28030,12 +28030,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -28050,12 +28050,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>428</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>7590</t>
+          <t>6638</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -28065,12 +28065,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -28085,12 +28085,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>3536</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>12011</t>
+          <t>12024</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -28100,7 +28100,7 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -28128,12 +28128,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>5235</t>
+          <t>5763</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>16756</t>
+          <t>18136</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -28143,12 +28143,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -28163,12 +28163,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>5812</t>
+          <t>5969</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>24747</t>
+          <t>27403</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -28178,12 +28178,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -28198,12 +28198,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>14471</t>
+          <t>15248</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>36358</t>
+          <t>38730</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -28213,12 +28213,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,89%</t>
         </is>
       </c>
     </row>
@@ -28241,12 +28241,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>102107</t>
+          <t>101319</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>114759</t>
+          <t>114301</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -28256,12 +28256,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -28276,12 +28276,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>128211</t>
+          <t>125899</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>147581</t>
+          <t>147039</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -28291,12 +28291,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -28311,12 +28311,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>235133</t>
+          <t>233323</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>258140</t>
+          <t>257710</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -28326,12 +28326,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,46%</t>
         </is>
       </c>
     </row>
@@ -28511,7 +28511,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>3015</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -28526,7 +28526,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -28546,7 +28546,7 @@
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>3561</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -28561,7 +28561,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -28810,12 +28810,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>1373</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>6962</t>
+          <t>6551</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -28825,12 +28825,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -28845,12 +28845,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>3379</t>
+          <t>3498</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>12317</t>
+          <t>12578</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -28860,12 +28860,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -28880,12 +28880,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>6065</t>
+          <t>6036</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>16720</t>
+          <t>16384</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -28895,12 +28895,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -28923,12 +28923,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>52004</t>
+          <t>52134</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>71042</t>
+          <t>70285</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -28938,12 +28938,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>54,63%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -28958,12 +28958,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>66720</t>
+          <t>67057</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>88326</t>
+          <t>88230</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -28973,12 +28973,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -28993,12 +28993,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>123401</t>
+          <t>123172</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>153029</t>
+          <t>153075</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -29008,12 +29008,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>54,12%</t>
         </is>
       </c>
     </row>
@@ -29036,12 +29036,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>54512</t>
+          <t>55028</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>74087</t>
+          <t>73219</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -29051,12 +29051,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -29071,12 +29071,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>58384</t>
+          <t>57646</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>79709</t>
+          <t>79878</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -29086,12 +29086,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -29106,12 +29106,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>119639</t>
+          <t>118727</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>148215</t>
+          <t>149000</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -29121,12 +29121,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,68%</t>
         </is>
       </c>
     </row>
@@ -29306,7 +29306,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>3415</t>
+          <t>3051</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -29321,7 +29321,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -29341,7 +29341,7 @@
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>3039</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -29356,7 +29356,7 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
     </row>
@@ -29492,12 +29492,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>1953</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>8431</t>
+          <t>8442</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -29507,7 +29507,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -29527,12 +29527,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>1558</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>12894</t>
+          <t>12506</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -29542,12 +29542,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -29562,12 +29562,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>5135</t>
+          <t>5232</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>17536</t>
+          <t>16828</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -29582,7 +29582,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -29605,12 +29605,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>21786</t>
+          <t>22247</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>39865</t>
+          <t>39751</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -29620,12 +29620,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -29640,12 +29640,12 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>44196</t>
+          <t>45121</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>71293</t>
+          <t>70735</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -29655,12 +29655,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -29675,12 +29675,12 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>71179</t>
+          <t>70615</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>103903</t>
+          <t>102454</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -29690,12 +29690,12 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -29718,12 +29718,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>139015</t>
+          <t>136470</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>246316</t>
+          <t>236877</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -29733,12 +29733,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -29753,12 +29753,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>147044</t>
+          <t>143449</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>192030</t>
+          <t>189261</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -29768,12 +29768,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -29788,12 +29788,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>297802</t>
+          <t>296794</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>415203</t>
+          <t>400601</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -29803,12 +29803,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>28,67%</t>
         </is>
       </c>
     </row>
@@ -29831,12 +29831,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>386255</t>
+          <t>389174</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>479913</t>
+          <t>481303</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -29846,12 +29846,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -29866,12 +29866,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>491430</t>
+          <t>490860</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>538922</t>
+          <t>540340</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -29881,12 +29881,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -29901,12 +29901,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>898558</t>
+          <t>903231</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>1004536</t>
+          <t>1004248</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -29916,12 +29916,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,87%</t>
         </is>
       </c>
     </row>
